--- a/excel/Rontgen.xlsx
+++ b/excel/Rontgen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-react\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Rontgen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCC6658-64F0-4AF2-B7A7-F1CA71E725DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB667939-4C95-49D3-A3CF-A053D4A6A1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>LTV max, %</t>
-  </si>
-  <si>
-    <t>Investuota viso</t>
   </si>
   <si>
     <t>Sutartis</t>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>Eur.</t>
+  </si>
+  <si>
+    <t>Investuota, Eur</t>
   </si>
 </sst>
 </file>
@@ -1568,7 +1568,7 @@
       <c r="F1" s="29"/>
       <c r="G1" s="30"/>
       <c r="H1" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I1" s="31"/>
       <c r="J1" s="31"/>
@@ -1576,17 +1576,17 @@
       <c r="L1" s="31"/>
       <c r="M1" s="31"/>
       <c r="O1" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P1" s="29"/>
       <c r="Q1" s="29"/>
       <c r="R1" s="30"/>
       <c r="S1" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T1" s="27"/>
       <c r="U1" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V1" s="26"/>
       <c r="W1" s="26"/>
@@ -1594,37 +1594,37 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="E2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="17" t="s">
-        <v>47</v>
-      </c>
       <c r="I2" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="17" t="s">
-        <v>57</v>
-      </c>
       <c r="K2" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>0</v>
@@ -1633,16 +1633,16 @@
         <v>5</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S2" s="7" t="s">
         <v>0</v>
@@ -1651,19 +1651,19 @@
         <v>5</v>
       </c>
       <c r="U2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="V2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="V2" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="W2" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="X2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="AC2" s="9" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J3" s="11">
         <f ca="1">'Riverland III butai VI, Vilnius'!B13</f>
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K3" s="11" t="str">
         <f ca="1">'Riverland III butai VI, Vilnius'!S3</f>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="X3" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>7.2525039315223694E-2</v>
+        <v>7.1880272030830403E-2</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Riverland III butai VI, Vilnius'!AA2</f>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J4" s="11">
         <f ca="1">'Panemunės apartamentai IX'!B13</f>
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K4" s="11" t="str">
         <f ca="1">'Panemunės apartamentai IX'!S3</f>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="J5" s="11">
         <f ca="1">'Spanguolių takai XXXVIII, Riešė'!B13</f>
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K5" s="11" t="str">
         <f ca="1">'Spanguolių takai XXXVIII, Riešė'!S3</f>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="J6" s="11">
         <f ca="1">'Pylimo g. 57 butai II, Vilnius'!B13</f>
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K6" s="11" t="str">
         <f ca="1">'Pylimo g. 57 butai II, Vilnius'!S3</f>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J8" s="11">
         <f ca="1">'UAB "NT reikalas" projektai VI'!B13</f>
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K8" s="11" t="str">
         <f ca="1">'UAB "NT reikalas" projektai VI'!S3</f>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="J9" s="11">
         <f ca="1">'Kaip Niujorke XXXVIII, Vilnius'!B13</f>
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K9" s="11" t="str">
         <f ca="1">'Kaip Niujorke XXXVIII, Vilnius'!S3</f>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="J10" s="11">
         <f ca="1">'UAB „Dear Home" projektai XV'!B13</f>
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K10" s="11" t="str">
         <f ca="1">'UAB „Dear Home" projektai XV'!S3</f>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J11" s="11">
         <f ca="1">'Laikas mėtoms VII, Vilnius'!B13</f>
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K11" s="11" t="str">
         <f ca="1">'Laikas mėtoms VII, Vilnius'!S3</f>
@@ -2538,7 +2538,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3">
         <v>20250418</v>
@@ -2559,13 +2559,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="28" t="s">
         <v>0</v>
@@ -2576,22 +2576,22 @@
       </c>
       <c r="P1" s="30"/>
       <c r="Q1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="32" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>41</v>
       </c>
       <c r="Y1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -2599,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" s="12">
         <v>46023</v>
@@ -2627,16 +2627,16 @@
         <v>0</v>
       </c>
       <c r="M2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -2769,7 +2769,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="12">
         <v>46296</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <v>46335</v>
@@ -2990,11 +2990,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="12"/>
       <c r="D14" s="9"/>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -3694,7 +3694,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3">
         <v>20250529</v>
@@ -3715,13 +3715,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="28" t="s">
         <v>0</v>
@@ -3732,22 +3732,22 @@
       </c>
       <c r="P1" s="30"/>
       <c r="Q1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="32" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>41</v>
       </c>
       <c r="Y1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -3755,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="12">
         <v>46023</v>
@@ -3783,16 +3783,16 @@
         <v>0</v>
       </c>
       <c r="M2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -3925,7 +3925,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="12">
         <v>46296</v>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <v>46339</v>
@@ -4143,11 +4143,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="12"/>
       <c r="D14" s="9"/>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -4842,25 +4842,25 @@
         <v>9</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -5204,7 +5204,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="23">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="K200" s="24">
         <f>Overview!U3</f>
@@ -5258,13 +5258,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="28" t="s">
         <v>0</v>
@@ -5275,22 +5275,22 @@
       </c>
       <c r="P1" s="30"/>
       <c r="Q1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="32" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>41</v>
       </c>
       <c r="Y1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -5298,7 +5298,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="12">
         <v>46296</v>
@@ -5314,16 +5314,16 @@
         <v/>
       </c>
       <c r="M2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -5432,7 +5432,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="12">
         <v>46569</v>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -5622,7 +5622,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <v>46587</v>
@@ -5649,11 +5649,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -5677,7 +5677,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="12"/>
       <c r="D14" s="9"/>
@@ -5702,7 +5702,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -6360,7 +6360,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3">
         <v>20250804</v>
@@ -6381,13 +6381,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="28" t="s">
         <v>0</v>
@@ -6398,22 +6398,22 @@
       </c>
       <c r="P1" s="30"/>
       <c r="Q1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="32" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>41</v>
       </c>
       <c r="Y1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -6421,7 +6421,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="12">
         <v>46296</v>
@@ -6437,16 +6437,16 @@
         <v/>
       </c>
       <c r="M2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -6555,7 +6555,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="12">
         <v>46569</v>
@@ -6718,7 +6718,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -6745,7 +6745,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <v>46593</v>
@@ -6772,11 +6772,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="12"/>
       <c r="D14" s="9"/>
@@ -6825,7 +6825,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -7476,7 +7476,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3">
         <v>20230414</v>
@@ -7497,13 +7497,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="28" t="s">
         <v>0</v>
@@ -7514,22 +7514,22 @@
       </c>
       <c r="P1" s="30"/>
       <c r="Q1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="32" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>41</v>
       </c>
       <c r="Y1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -7537,7 +7537,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="12">
         <v>46296</v>
@@ -7553,16 +7553,16 @@
         <v/>
       </c>
       <c r="M2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -7671,7 +7671,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="5"/>
@@ -7830,7 +7830,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -7857,7 +7857,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <v>46412</v>
@@ -7884,11 +7884,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -7912,7 +7912,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="12"/>
       <c r="D14" s="9"/>
@@ -7937,7 +7937,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -8588,7 +8588,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3">
         <v>20220721</v>
@@ -8609,13 +8609,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="28" t="s">
         <v>0</v>
@@ -8626,22 +8626,22 @@
       </c>
       <c r="P1" s="30"/>
       <c r="Q1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="32" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>41</v>
       </c>
       <c r="Y1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -8649,7 +8649,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="12">
         <v>46113</v>
@@ -8677,16 +8677,16 @@
         <v>0</v>
       </c>
       <c r="M2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -8809,7 +8809,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="12">
         <v>46296</v>
@@ -8980,7 +8980,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -9007,7 +9007,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <v>46399</v>
@@ -9034,11 +9034,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -9062,7 +9062,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="12"/>
       <c r="D14" s="9"/>
@@ -9087,7 +9087,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -9741,7 +9741,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3">
         <v>20251031</v>
@@ -9762,13 +9762,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="28" t="s">
         <v>0</v>
@@ -9779,22 +9779,22 @@
       </c>
       <c r="P1" s="30"/>
       <c r="Q1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="32" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>41</v>
       </c>
       <c r="Y1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -9802,7 +9802,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" s="12">
         <v>46023</v>
@@ -9830,16 +9830,16 @@
         <v>0</v>
       </c>
       <c r="M2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -9972,7 +9972,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="12">
         <v>46342</v>
@@ -10145,7 +10145,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -10172,7 +10172,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <v>46342</v>
@@ -10199,7 +10199,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="11" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -10227,7 +10227,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="12">
         <v>46212</v>
@@ -10254,7 +10254,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -10904,7 +10904,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3">
         <v>20250715</v>
@@ -10925,13 +10925,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="28" t="s">
         <v>0</v>
@@ -10942,22 +10942,22 @@
       </c>
       <c r="P1" s="30"/>
       <c r="Q1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="32" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>41</v>
       </c>
       <c r="Y1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -10965,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="12">
         <v>46023</v>
@@ -10993,16 +10993,16 @@
         <v>0</v>
       </c>
       <c r="M2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -11135,7 +11135,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="12">
         <v>46296</v>
@@ -11302,7 +11302,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -11329,7 +11329,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <v>46325</v>
@@ -11356,11 +11356,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -11384,7 +11384,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="12"/>
       <c r="D14" s="9"/>
@@ -11409,7 +11409,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -12059,7 +12059,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3">
         <v>20230607</v>
@@ -12080,13 +12080,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="28" t="s">
         <v>0</v>
@@ -12097,22 +12097,22 @@
       </c>
       <c r="P1" s="30"/>
       <c r="Q1" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="32" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>41</v>
       </c>
       <c r="Y1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -12120,7 +12120,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" s="12">
         <v>46023</v>
@@ -12148,16 +12148,16 @@
         <v>0</v>
       </c>
       <c r="M2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -12290,7 +12290,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="12">
         <v>46204</v>
@@ -12485,7 +12485,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <v>46304</v>
@@ -12539,11 +12539,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -12567,7 +12567,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="12"/>
       <c r="D14" s="9"/>
@@ -12592,7 +12592,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>

--- a/excel/Rontgen.xlsx
+++ b/excel/Rontgen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Rontgen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB667939-4C95-49D3-A3CF-A053D4A6A1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DF5237-A94F-4DBA-86A9-5B07AF18C157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J3" s="11">
         <f ca="1">'Riverland III butai VI, Vilnius'!B13</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K3" s="11" t="str">
         <f ca="1">'Riverland III butai VI, Vilnius'!S3</f>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="X3" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>7.1880272030830403E-2</v>
+        <v>7.0934286713600164E-2</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Riverland III butai VI, Vilnius'!AA2</f>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J4" s="11">
         <f ca="1">'Panemunės apartamentai IX'!B13</f>
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K4" s="11" t="str">
         <f ca="1">'Panemunės apartamentai IX'!S3</f>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="J5" s="11">
         <f ca="1">'Spanguolių takai XXXVIII, Riešė'!B13</f>
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K5" s="11" t="str">
         <f ca="1">'Spanguolių takai XXXVIII, Riešė'!S3</f>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="J6" s="11">
         <f ca="1">'Pylimo g. 57 butai II, Vilnius'!B13</f>
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K6" s="11" t="str">
         <f ca="1">'Pylimo g. 57 butai II, Vilnius'!S3</f>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J8" s="11">
         <f ca="1">'UAB "NT reikalas" projektai VI'!B13</f>
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K8" s="11" t="str">
         <f ca="1">'UAB "NT reikalas" projektai VI'!S3</f>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="J9" s="11">
         <f ca="1">'Kaip Niujorke XXXVIII, Vilnius'!B13</f>
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K9" s="11" t="str">
         <f ca="1">'Kaip Niujorke XXXVIII, Vilnius'!S3</f>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="J10" s="11">
         <f ca="1">'UAB „Dear Home" projektai XV'!B13</f>
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="K10" s="11" t="str">
         <f ca="1">'UAB „Dear Home" projektai XV'!S3</f>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J11" s="11">
         <f ca="1">'Laikas mėtoms VII, Vilnius'!B13</f>
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="K11" s="11" t="str">
         <f ca="1">'Laikas mėtoms VII, Vilnius'!S3</f>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -5204,7 +5204,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="23">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
+        <v>46235</v>
       </c>
       <c r="K200" s="24">
         <f>Overview!U3</f>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>

--- a/excel/Rontgen.xlsx
+++ b/excel/Rontgen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Rontgen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.08.08\Rontgen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DF5237-A94F-4DBA-86A9-5B07AF18C157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA966AD-2023-4B74-B918-CE388506911F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -445,6 +445,18 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -453,23 +465,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1558,39 +1558,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="31" t="s">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="O1" s="28" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="O1" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="25" t="s">
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="27"/>
-      <c r="U1" s="25" t="s">
+      <c r="T1" s="31"/>
+      <c r="U1" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="27"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="31"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J3" s="11">
         <f ca="1">'Riverland III butai VI, Vilnius'!B13</f>
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K3" s="11" t="str">
         <f ca="1">'Riverland III butai VI, Vilnius'!S3</f>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P3" s="5">
         <f>SUM(G3:G200)-S3</f>
-        <v>704.17</v>
+        <v>700</v>
       </c>
       <c r="Q3" s="5">
         <f>Pinigai!H2</f>
@@ -1732,31 +1732,31 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>0.50000000000011369</v>
+        <v>4.7000000000000455</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
-        <v>195.83</v>
+        <v>200</v>
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>26.46</v>
+        <v>26.490000000000002</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>704.67000000000007</v>
+        <v>704.7</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>30.460000000000036</v>
+        <v>30.490000000000009</v>
       </c>
       <c r="W3" s="15">
         <f>(U3-O3)/O3</f>
-        <v>4.5178801856988228E-2</v>
+        <v>4.5223298378843396E-2</v>
       </c>
       <c r="X3" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>7.0934286713600164E-2</v>
+        <v>6.2502047419548026E-2</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Riverland III butai VI, Vilnius'!AA2</f>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J4" s="11">
         <f ca="1">'Panemunės apartamentai IX'!B13</f>
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="K4" s="11" t="str">
         <f ca="1">'Panemunės apartamentai IX'!S3</f>
@@ -1852,13 +1852,13 @@
         <f>'Spanguolių takai XXXVIII, Riešė'!B12</f>
         <v>46304</v>
       </c>
-      <c r="I5" s="20" t="str">
+      <c r="I5" s="20">
         <f>'Spanguolių takai XXXVIII, Riešė'!R3</f>
-        <v/>
-      </c>
-      <c r="J5" s="11">
+        <v>46252</v>
+      </c>
+      <c r="J5" s="11" t="str">
         <f ca="1">'Spanguolių takai XXXVIII, Riešė'!B13</f>
-        <v>69</v>
+        <v/>
       </c>
       <c r="K5" s="11" t="str">
         <f ca="1">'Spanguolių takai XXXVIII, Riešė'!S3</f>
@@ -1866,11 +1866,11 @@
       </c>
       <c r="L5" s="5">
         <f>'Spanguolių takai XXXVIII, Riešė'!N3</f>
-        <v>95.830000000000013</v>
+        <v>100.00000000000001</v>
       </c>
       <c r="M5" s="5">
         <f>'Spanguolių takai XXXVIII, Riešė'!P3</f>
-        <v>4.3099999999999996</v>
+        <v>4.34</v>
       </c>
       <c r="AC5" s="5" t="str">
         <f ca="1">'Spanguolių takai XXXVIII, Riešė'!AA2</f>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="J6" s="11">
         <f ca="1">'Pylimo g. 57 butai II, Vilnius'!B13</f>
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="K6" s="11" t="str">
         <f ca="1">'Pylimo g. 57 butai II, Vilnius'!S3</f>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J8" s="11">
         <f ca="1">'UAB "NT reikalas" projektai VI'!B13</f>
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="K8" s="11" t="str">
         <f ca="1">'UAB "NT reikalas" projektai VI'!S3</f>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="J9" s="11">
         <f ca="1">'Kaip Niujorke XXXVIII, Vilnius'!B13</f>
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="K9" s="11" t="str">
         <f ca="1">'Kaip Niujorke XXXVIII, Vilnius'!S3</f>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="J10" s="11">
         <f ca="1">'UAB „Dear Home" projektai XV'!B13</f>
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="K10" s="11" t="str">
         <f ca="1">'UAB „Dear Home" projektai XV'!S3</f>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J11" s="11">
         <f ca="1">'Laikas mėtoms VII, Vilnius'!B13</f>
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="K11" s="11" t="str">
         <f ca="1">'Laikas mėtoms VII, Vilnius'!S3</f>
@@ -2502,7 +2502,7 @@
   <hyperlinks>
     <hyperlink ref="C3" location="'Riverland III butai (6)'!A1" display="'Riverland III butai (6)'!A1" xr:uid="{4D570A1C-4B37-4100-B350-716432AD4918}"/>
     <hyperlink ref="C4" location="'Panemunės apartamentai (9)'!A1" display="'Panemunės apartamentai (9)'!A1" xr:uid="{6036774D-9777-4AF7-83F7-56D558CBB834}"/>
-    <hyperlink ref="C5" location="'Spanguolių takai (38)'!A1" display="'Spanguolių takai (38)'!A1" xr:uid="{3B3D5039-CE6F-4660-9342-AD3DEC2102EE}"/>
+    <hyperlink ref="C5" location="'Spanguolių takai XXXVIII, Riešė'!A1" display="'Spanguolių takai XXXVIII, Riešė'!A1" xr:uid="{3B3D5039-CE6F-4660-9342-AD3DEC2102EE}"/>
     <hyperlink ref="C6" location="'Pylimo g. 57 butai (2)'!A1" display="'Pylimo g. 57 butai (2)'!A1" xr:uid="{E7702D2C-76CD-4E0C-BFD5-0D530CFCB9A2}"/>
     <hyperlink ref="C7" location="'ROOTHAUS (1)'!A1" display="'ROOTHAUS (1)'!A1" xr:uid="{791EC8ED-11BE-492B-B2EB-A5920ED9056D}"/>
     <hyperlink ref="C8" location="'UAB &quot;NT reikalas&quot; projektai VI'!A1" display="'UAB &quot;NT reikalas&quot; projektai VI'!A1" xr:uid="{2E431F7A-3C8E-4BEF-98A8-E19DC8DB4C11}"/>
@@ -2567,21 +2567,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -2638,9 +2638,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45964</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -3723,21 +3723,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -3794,9 +3794,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45964</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -5204,11 +5204,11 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="23">
         <f ca="1">TODAY()</f>
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="K200" s="24">
         <f>Overview!U3</f>
-        <v>704.67000000000007</v>
+        <v>704.7</v>
       </c>
     </row>
   </sheetData>
@@ -5266,21 +5266,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -5325,9 +5325,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>46217</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -6389,21 +6389,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -6448,9 +6448,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>46216</v>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -7505,21 +7505,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -7564,9 +7564,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>46185</v>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -8617,21 +8617,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -8688,9 +8688,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>46027</v>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -9770,21 +9770,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -9841,9 +9841,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45972</v>
@@ -10933,21 +10933,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -11004,9 +11004,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45967</v>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -12041,6 +12041,9 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12088,21 +12091,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -12159,9 +12162,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45965</v>
@@ -12213,23 +12216,23 @@
       </c>
       <c r="N3" s="5">
         <f>G42</f>
-        <v>95.830000000000013</v>
+        <v>100.00000000000001</v>
       </c>
       <c r="O3" s="5">
         <f>F42</f>
-        <v>4.3099999999999996</v>
+        <v>4.34</v>
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>4.3099999999999996</v>
-      </c>
-      <c r="Q3" s="15" t="str">
+        <v>4.34</v>
+      </c>
+      <c r="Q3" s="15">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
-        <v/>
-      </c>
-      <c r="R3" s="12" t="str">
+        <v>7.0387747883796689E-2</v>
+      </c>
+      <c r="R3" s="12">
         <f>IF(M3=N3,B14,"")</f>
-        <v/>
+        <v>46252</v>
       </c>
       <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
@@ -12380,14 +12383,24 @@
       <c r="E7" s="5">
         <v>0</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12">
+        <v>46252</v>
+      </c>
+      <c r="K7" s="11">
+        <f t="shared" si="0"/>
+        <v>-44</v>
       </c>
       <c r="Y7" s="12">
         <f t="shared" si="1"/>
@@ -12411,18 +12424,28 @@
       <c r="E8" s="5">
         <v>100</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="F8" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G8" s="5">
+        <v>4.17</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
+        <v>46252</v>
+      </c>
+      <c r="K8" s="11">
+        <f t="shared" si="0"/>
+        <v>-52</v>
       </c>
       <c r="Y8" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46252</v>
       </c>
       <c r="Z8" s="5">
         <f t="shared" si="2"/>
@@ -12449,11 +12472,11 @@
       </c>
       <c r="Y9" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46252</v>
       </c>
       <c r="Z9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
@@ -12541,9 +12564,9 @@
       <c r="A13" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="11" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>69</v>
+        <v/>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -12569,7 +12592,9 @@
       <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="12"/>
+      <c r="B14" s="12">
+        <v>46252</v>
+      </c>
       <c r="D14" s="9"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -12594,9 +12619,9 @@
       <c r="A15" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="3" t="str">
+      <c r="B15" s="3">
         <f>IF(M3=N3,B14-B12,"")</f>
-        <v/>
+        <v>-52</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="5"/>
@@ -13174,15 +13199,15 @@
       </c>
       <c r="F42" s="5">
         <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
-        <v>4.3099999999999996</v>
+        <v>4.34</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="3"/>
-        <v>95.830000000000013</v>
+        <v>100.00000000000001</v>
       </c>
       <c r="H42" s="5">
         <f t="shared" si="3"/>
-        <v>4.3099999999999996</v>
+        <v>4.34</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="3"/>
